--- a/Security/Product-Based-Templates/AgenticAI.xlsx
+++ b/Security/Product-Based-Templates/AgenticAI.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECF8BD91-5064-334D-97FD-BE319C6E38F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-37440" yWindow="2440" windowWidth="37420" windowHeight="17440" xr2:uid="{1397FCF7-9C7E-D04C-AE64-26F641C0300C}"/>
+    <workbookView xWindow="6520" yWindow="4900" windowWidth="28040" windowHeight="17440" xr2:uid="{1397FCF7-9C7E-D04C-AE64-26F641C0300C}"/>
   </bookViews>
   <sheets>
     <sheet name="Capabilities" sheetId="1" r:id="rId1"/>
